--- a/Data/C05 Figures.xlsx
+++ b/Data/C05 Figures.xlsx
@@ -11162,6 +11162,20 @@
         <v>3.57</v>
       </c>
     </row>
+    <row r="767">
+      <c r="A767" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B767" t="n">
+        <v>-1.42</v>
+      </c>
+      <c r="C767" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="D767" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Data/C05 Figures.xlsx
+++ b/Data/C05 Figures.xlsx
@@ -11176,6 +11176,20 @@
         <v>3.6</v>
       </c>
     </row>
+    <row r="768">
+      <c r="A768" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B768" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="C768" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="D768" t="n">
+        <v>3.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Data/C05 Figures.xlsx
+++ b/Data/C05 Figures.xlsx
@@ -11190,6 +11190,20 @@
         <v>3.61</v>
       </c>
     </row>
+    <row r="769">
+      <c r="A769" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B769" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="C769" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="D769" t="n">
+        <v>3.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -12313,13 +12327,13 @@
         <v>2023</v>
       </c>
       <c r="B80" t="n">
-        <v>-0.26440366099971</v>
+        <v>-0.253309977974512</v>
       </c>
       <c r="C80" t="n">
-        <v>0.744872944532259</v>
+        <v>0.736333557151775</v>
       </c>
       <c r="D80" t="n">
-        <v>0.48046928353255</v>
+        <v>0.483023579177263</v>
       </c>
     </row>
     <row r="81">
@@ -12327,13 +12341,27 @@
         <v>2024</v>
       </c>
       <c r="B81" t="n">
-        <v>-0.312356786168218</v>
+        <v>-0.27843294190766</v>
       </c>
       <c r="C81" t="n">
-        <v>0.795710606002604</v>
+        <v>0.760174434969862</v>
       </c>
       <c r="D81" t="n">
-        <v>0.483353819834386</v>
+        <v>0.481741493062202</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B82" t="n">
+        <v>-0.255415119324549</v>
+      </c>
+      <c r="C82" t="n">
+        <v>0.748859630056128</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0.493444510731579</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C05 Figures.xlsx
+++ b/Data/C05 Figures.xlsx
@@ -11204,6 +11204,20 @@
         <v>3.61</v>
       </c>
     </row>
+    <row r="770">
+      <c r="A770" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B770" t="n">
+        <v>-1.31</v>
+      </c>
+      <c r="C770" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="D770" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -12355,13 +12369,13 @@
         <v>2025</v>
       </c>
       <c r="B82" t="n">
-        <v>-0.255415119324549</v>
+        <v>-0.255274081528828</v>
       </c>
       <c r="C82" t="n">
-        <v>0.748859630056128</v>
+        <v>0.748446116902298</v>
       </c>
       <c r="D82" t="n">
-        <v>0.493444510731579</v>
+        <v>0.49317203537347</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C05 Figures.xlsx
+++ b/Data/C05 Figures.xlsx
@@ -11218,6 +11218,20 @@
         <v>3.6</v>
       </c>
     </row>
+    <row r="771">
+      <c r="A771" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B771" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="C771" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="D771" t="n">
+        <v>3.66</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
